--- a/osint_cyber_paper_library_206_v7_enriched.xlsx
+++ b/osint_cyber_paper_library_206_v7_enriched.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Decision Analytics Journal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>This paper appears to address cloud-based cti platform within the broader area of cyber threat intelligence. It likely focuses on detecting, classifying, or predicting security-relevant events or indicators from open or semi-open data sources. Relevant domains include Cyber threat intelligence; Real-time detection.</t>
+          <t>The extraction of cyber threat intelligence (CTI) from open sources is a rapidly expanding defensive strategy that enhances the resilience of both Information Technology (IT) and Operational Technology (OT) environments against large-scale cyber-attacks. However, for most organizations, collecting actionable CTI remains both a technical bottleneck and a black box. While previous research has focused on improving individual components of the extraction process, the community lacks open-source platforms for deploying streaming CTI data pipelines in the wild. This study proposes an efficient platform capable of processing compute-intensive data pipelines, based on cloud computing, for real-time detection, collection, and sharing of CTI from various online sources. We developed a prototype platform (TSTEM) with a containerized microservice architecture that uses Tweepy, Scrapy, Terraform, Elasticsearch, Logstash, and Kibana (ELK), Kafka, and Machine Learning Operations (MLOps) to autonomously search, extract, and index indicators of compromise (IOCs) in the wild. Moreover, the provisioning, monitoring, and management of the platform are achieved through infrastructure as code (IaC). Custom focus-crawlers collect web content, processed by a first-level classifier to identify potential IOCs. Relevant content advances to a second level for further examination. State-of-the-art natural language processing (NLP) models are used for classification and entity extraction, enhancing the IOC extraction methodology. Our results indicate these models exhibit high accuracy (exceeding 98%) in classification and extraction tasks, achieving this performance within less than a minute. The system’s effectiveness is due to a finely-tuned IOC extraction method that operates at multiple stages, ensuring precise identification with low false positives. • Use containerized microservice architecture for real-time cyber threat intelligence detection from online sources. • Implement custom focus crawlers to efficiently and accurately extract indicators of compromise (IOCs). • Propose an innovative method for autonomous search and extraction of IOCs using transformer-based algorithms. • Use infrastructure as a code for enhancing the automation of the cyber threat intelligence collection process. • Demonstrate scalable and efficient cloud-based data pipelines for handling computationally demanding tasks.</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2779,9 +2779,21 @@
           <t>CTI; Platform; Real-time detection; Cloud computing; Cyber threat intelligence; Web; Social media; Feeds; Threat intelligence; Cloud-based CTI platform</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.dajour.2025.100545</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2794,7 +2806,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fifeen Sufi et al.</t>
+          <t>Fahim Sufi</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2802,7 +2814,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Natural Language Processing Journal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2852,7 +2864,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>venue normalized; DOI completed; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; DOI completed; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2870,7 +2882,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>This paper appears to address llm-assisted cyber-event extraction within the broader area of cyber threat intelligence. It likely contributes to threat intelligence collection, indicator extraction, or vulnerability-focused analysis using open-source data. Relevant domains include Cyber threat intelligence.</t>
+          <t>In contemporary discourse, the pervasive influences of Generative Pre-Trained (GPT) and Large Language Models (LLM) are evident, showcasing diverse applications. GPT-based technologies, transcending mere summarization, exhibit adeptness in discerning critical information from extensive textual corpuses. Through prudent extraction of semantically meaningful content from textual representations, GPT technologies engender automated feature extraction, a departure from the fallible manual extraction methodologies. This study posits an innovative paradigm for extracting multidimensional cyber threat-related features from textual depictions of cyber events, leveraging the prowess of GPT. These extracted features serve as inputs for artificial intelligence (AI) and deep learning algorithms, including Convolutional Neural Network (CNN), Decomposition analysis, and Natural Language Processing (NLP)-based modalities tailored for non-technical cyber strategists. The proposed framework empowers cyber strategists or analysts to articulate inquiries regarding historical cyber incidents in plain English, with the NLP-based interaction facet of the system proffering cogent AI-driven insights in natural language. Furthermore, salient insights, often elusive in dynamic visualizations, are succinctly presented in plain language. Empirical validation of the entire system ensued through autonomous acquisition of semantically enriched contextual information concerning 214 major cyber incidents spanning from 2016 to 2023. GPT-based responses on Actor Type, Target, Attack Source (i.e., Country Originating Attack), Attack Destination (i.e., Targeted Country), Attack Level, Attack Type, and Attack Timeline, underwent critical AI-driven analysis. This comprehensive 7-dimensional information gleaned from the corpus of 214 incidents yielded a corpus of 1498 informative outputs, attaining a commendable precision of 96%, a recall rate of 98%, and an F1-Score of 97%.</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2878,9 +2890,21 @@
           <t>LLM; GPT; OSINT; Cyber events; Feature extraction; Cyber threat intelligence; Textual cyber-event reports; CTI; AI; LLM-assisted cyber-event extraction</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.nlp.2024.100074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2901,7 +2925,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Journal of Information Security and Applications</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2951,7 +2975,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2969,7 +2993,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>This paper appears to address cti sharing survey within the broader area of cyber threat intelligence. It likely synthesizes prior literature, methods, and application areas, with particular relevance for analysts building OSINT-informed cyber investigation workflows. Relevant domains include Cyber threat intelligence.</t>
+          <t>Cyber Threat Intelligence (CTI) is essential knowledge concerning cyber and physical threats aimed at mitigating potential cyber attacks. The rapid evolution of Information and Communications Technology (ICT), the Internet of Things (IoT), and Industry 5.0 has spawned a multitude of sources regarding current or potential cyber threats against organizations. Consequently, CTI sharing among organizations holds considerable promise for facilitating swift responses to attacks and enabling mutual benefits through active participation. However, exchanging CTI among different organizations poses significant challenges, including legal and regulatory obligations, interoperability standards, and data reliability. The current CTI sharing landscape remains inadequately explored, hindering a comprehensive examination of organizations’ critical needs and the challenges they encounter during CTI sharing. This paper presents a comprehensive survey on CTI sharing, beginning with an exploration of CTI fundamentals and its advancements in assessing cyber and physical threats and threat actors from various perspectives. For instance, we discuss the benefits of CTI, its applications, and diverse CTI sharing architectures. Additionally, we extensively discuss a list of CTI sharing challenges and evaluate how available CTI sharing proposals address these challenges. Finally, we provide an inventory of unique future research directions to offer insightful guidelines for CTI sharing.</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2977,9 +3001,21 @@
           <t>CTI; Survey; Sharing; Standards; Cyber threat intelligence; Mixed; Threat intelligence; CTI sharing survey</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jisa.2024.103786</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2992,7 +3028,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Guanghui Wang; Xin Chen et al.</t>
+          <t>Gaosheng Wang; Peipei Liu; Jintao Huang; Haoyu Bin; Xi Wang; Hongsong Zhu</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3000,7 +3036,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Computers &amp;amp; Security</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3050,7 +3086,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>venue normalized; DOI completed; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; DOI completed; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -3076,9 +3112,17 @@
           <t>CTI; NLP; Entity extraction; Relation extraction; Knowledge graph; Cyber threat intelligence; Threat reports; Threat intelligence; Entity and relation extraction from CTI reports</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.cose.2024.103824</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3091,7 +3135,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prasasthy Balasubramanian; Sadaf Nazari; Danial Khosh Kholgh; Alireza Mahmoodi; Justin Seby; Panos Kostakos</t>
+          <t>Saeid Sheikhi; Panos Kostakos</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3099,7 +3143,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Computers &amp;amp; Security</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3149,7 +3193,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -3167,7 +3211,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>This paper appears to address streaming cti collection platform within the broader area of cyber threat intelligence. It likely contributes to threat intelligence collection, indicator extraction, or vulnerability-focused analysis using open-source data. Relevant domains include Cyber threat intelligence; Security operations.</t>
+          <t>In recent years, the exponential growth of internet usage worldwide has created a conducive environment for the expansion of malicious activities. Among these threats, malicious websites pose a significant risk to individual users and corporations. This paper presents a robust and efficient model for the detection of various types of malicious websites with high accuracy in the process. The proposed approach employs a two-step process. Firstly, a feature selection method based on the Firefly algorithm is utilized to identify the most relevant features. Subsequently, an optimized version of the XGBoost algorithm is applied to classify websites based on the selected features. Optimization of XGBoost's parameters is achieved through the Particle Swarm Optimization (PSO) algorithm to enhance its performance. To assess the efficacy of the introduced model, the model is evaluated against several benchmark classification algorithms using a dataset comprising over 36,000 websites. In binary classification, the introduced model surpasses other benchmark methods with a significant 98.42% classification accuracy and an F1 score of 0.984. For multiclass problem classification, it consistently achieves over 98% accuracy in each class. The test results highlight the proposed model's robust performance, characterized by exceptional classification accuracy and F1-measure rates. It demonstrates the capability to detect various types of malicious websites with high precision and minimal false error rates.</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -3175,9 +3219,21 @@
           <t>CTI; Platform; IOC extraction; Streaming; MLOps; Cyber threat intelligence; Security operations; Web; Social media; Feeds</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.cose.2024.103885</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3190,7 +3246,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andrea Tundis; Giuseppe Casalinuovo; Nicola Mazzocca; Francesco Roli</t>
+          <t>Andrea Tundis; Samuel Ruppert; Max Mühlhäuser</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3198,7 +3254,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Computers &amp;amp; Security</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3248,7 +3304,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>venue normalized; DOI completed; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; DOI completed; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -3276,9 +3332,17 @@
           <t>CTI; Source quality; Assessment; Automation; Cyber threat intelligence; Open-source CTI feeds; Threat intelligence; CTI source assessment</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.cose.2021.102576</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3289,15 +3353,17 @@
           <t>Efficient Data Noise-Reduction for Cyber Threat intelligence System</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Seonghyeon Gong; Changhoon Lee</t>
+        </is>
       </c>
       <c r="D8" t="n">
         <v>2021</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Springer</t>
+          <t>Lecture Notes in Electrical Engineering</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3347,7 +3413,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -3373,9 +3439,17 @@
           <t>Cyber Threat Intelligence; Online Dataset; Security Operations; CTI; Threat intelligence</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/978-981-15-9343-7_83</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3386,15 +3460,17 @@
           <t>Open Source Intelligence for Malicious Behavior Discovery and Interpretation</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yi-Ting Huang; Chi Yu Lin; Ying-REN Guo; Kai-Chieh Lo; Yeali S. Sun; Meng Chang Chen</t>
+        </is>
       </c>
       <c r="D9" t="n">
         <v>2021</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>IEEE Transactions on Dependable and Secure Computing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3437,12 +3513,14 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10.1109/tdsc.2021.3119008</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>venue normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref search; OpenAlex search; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -3460,7 +3538,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>This paper appears to address cyber threat intelligence within the broader area of cyber threat intelligence. It likely develops or evaluates methods, workflows, or analytical models that support OSINT-enabled cybersecurity research or operational investigation. Relevant domains include Cyber Threat Intelligence; Security Operations.</t>
+          <t>Cyber threats are one of the most pressing issues in the digital age. There has been a consensus on deploying a proactive defense to effectively detect and respond to adversary threats. The key to success is understanding the characteristics of malware, including their activities and manipulated resources on the target machines. The MITRE ATT&amp;CK framework (ATT&amp;CK), a popular source of open source intelligence (OSINT), provides rich information and knowledge about adversary lifecycles and attack behaviors. The main challenges of this study involve knowledge collection from ATT&amp;CK, malicious behavior identification using deep learning, and the identification of associated API calls. A MITRE ATT&amp;CK based Malicious Behavior Analysis system (MAMBA) for Windows malware is proposed, which incorporates ATT&amp;CK knowledge and considers attentions on manipulated resources and malicious activities in the neural network model. To synchronize ATT&amp;CK updates in a timely manner, knowledge collection can be an automatic and incremental process. Given these features, MAMBA achieves the best performance of malicious behavior discovery among all the compared learning-based methods and rule-based approaches on all datasets; it also yields a highly interpretable mapping from the discovered malicious behaviors to relevant ATT&amp;CK techniques, as well as to the related API calls.</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3468,9 +3546,21 @@
           <t>Cyber Threat Intelligence; Online dataset; Security Operations; OSINT</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Crossref search; OpenAlex search</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/tdsc.2021.3119008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3481,15 +3571,17 @@
           <t>Automated Cyber Threat Intelligence Reports Classification for Early Warning of Cyber Attacks in Next Generation SOC</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wenzhuo Yang; Kwok-Yan Lam</t>
+        </is>
       </c>
       <c r="D10" t="n">
         <v>2020</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Springer</t>
+          <t>Lecture Notes in Computer Science</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3539,7 +3631,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -3565,9 +3657,17 @@
           <t>Cyber Threat Intelligence; Report Classification; Online dataset; Security Operations; CTI; Threat intelligence</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/978-3-030-41579-2_9</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3578,15 +3678,17 @@
           <t>Cyber Threats Prediction model based on Artificial Neural Networks using Quantification of Open Source Intelligence (OSINT)</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>육군사관학교 컴퓨터학과; Jongkwan Lee; Minam Moon; Kyuyong Shin; Sungrok Kang</t>
+        </is>
       </c>
       <c r="D11" t="n">
         <v>2020</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>e-Article</t>
+          <t>Jouranl of Information and Security</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3629,12 +3731,14 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>10.33778/kcsa.2020.20.3.115</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>venue normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref search; OpenAlex search; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3652,7 +3756,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>This paper appears to address cyber threat prediction within the broader area of cyber threat intelligence. It likely focuses on detecting, classifying, or predicting security-relevant events or indicators from open or semi-open data sources. Relevant domains include Security Operations; Cyber Threat Intelligence.</t>
+          <t>사이버공격은 최근 몇 년간 더욱 더 진화하고 있다. 이렇게 고도화, 정교화된 사이버위협에 대응하기 위한 최선의 대책 중 하나는 사이버 공격을 사전에 예측하는 것이다. 사이버위협을 예측하기 위해서는 많은 정보와 노력이 요구되며 최근 정보획득 의 핵심인 공개출처정보(Open Source Intelligence, OSINT)를 활용한다면 사이버위협을 보다 정확히 예측할 수 있을 것이다. 공개출처정보를 활용하여 사이버위협을 예측하기 위해서는 공개출처정보로부터 사이버위협 데이터베이스의 구축과 구축된 DB 에서 사이버위협을 평가할 수 있는 요소를 선정하는 것이 선행되어야 한다. 이를 위해 데이터마이닝 기법을 활용하여 DB를 구 축하고, 축적된 DB 요소 중 핵심요소에 대한 중요도를 AHP 기법으로 분석한 선행연구를 기초로 하였다. 본 연구에서는 공개 출처정보로부터 축적된 사이버공격 DB를 활용하여 사이버위협을 정량화할 수 있는 방안을 제시하고 인공신경망을 기반으로 한 사이버위협 예측 모델을 제안한다.</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -3660,9 +3764,21 @@
           <t>Cyber Threat Prediction; Online dataset; Security Operations; Cyber Threat Intelligence; OSINT; CTI; Network analysis</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Crossref search; OpenAlex search</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.33778/kcsa.2020.20.3.115</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3673,15 +3789,17 @@
           <t>Inductive and Deductive Reasoning to Assist in Cyber-Attack Prediction</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ericsson Marin; Mohammed Almukaynizi; Paulo Shakarian</t>
+        </is>
       </c>
       <c r="D12" t="n">
         <v>2020</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>2020 10th Annual Computing and Communication Workshop and Conference (CCWC)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3724,12 +3842,14 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10.1109/ccwc47524.2020.9031154</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>venue normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref search; OpenAlex search; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3747,7 +3867,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>This paper appears to address cyber attack prediction within the broader area of cyber threat intelligence. It likely focuses on detecting, classifying, or predicting security-relevant events or indicators from open or semi-open data sources. Relevant domains include Cyber Threat Intelligence; Security operations.</t>
+          <t>Information about cyber-attack planning has been increasingly shared by malicious hackers online, making what was once a hard-to-penetrate market becomes accessible to a wider population. Although this trend helps to produce a huge amount of malware, it also provides intelligence for defenders since the shared information can be leveraged as precursors of cyber-attacks. In this work, we apply Annotated Probabilistic Temporal (APT) logic into the cybersecurity domain to accomplish two tasks: 1) induct APT rules that correlate malicious hacking activity with enterprise attacks to predict imminent cyber incidents; 2) leverage a deductive approach that combines attack predictions for more accurate security warnings. Results demonstrate considerable prediction gains in F1 score (up to 150.24%) compared to the baseline when the pre-conditions of APT rules include socio-personal indicators of the hackers behind cyber incidents, and when the predictions made for a given day are combined using deduction (up to 182.38%). Those findings highlight how AI tools can empower proactive cyber defense</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -3755,9 +3875,21 @@
           <t>Cyber Attack Prediction; Online Dataset; Darkweb Forums; Emails; Cyber Threat Intelligence; Security operations; CTI</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Crossref search; OpenAlex search</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/ccwc47524.2020.9031154</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3768,15 +3900,17 @@
           <t>A supervised machine learning based approach for automatically extracting high-level threat intelligence from unstructured sources</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yumna Ghazi; Zahid Anwar; Rafia Mumtaz; Shahzad Saleem; Ali Tahir</t>
+        </is>
       </c>
       <c r="D13" t="n">
         <v>2018</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>2018 International Conference on Frontiers of Information Technology (FIT)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3819,12 +3953,14 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>10.1109/fit.2018.00030</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>venue normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref search; OpenAlex search; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3842,7 +3978,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>This paper appears to address cyber threat intelligence within the broader area of cyber threat intelligence. It likely contributes to threat intelligence collection, indicator extraction, or vulnerability-focused analysis using open-source data. Relevant domains include Security Operations; Cyber Threat Intelligence.</t>
+          <t>The last few years have seen a radical shift in the cyber defense paradigm from reactive to proactive, and this change is marked by the steadily increasing trend of Cyber Threat Intelligence (CTI) sharing. Currently, there are numerous Open Source Intelligence (OSINT) sources providing periodically updated threat feeds that are fed into various analytical solutions. At this point, there is an excessive amount of data being produced from such sources, both structured (STIX, OpenIOC, etc.) as well as unstructured (blacklists, etc.). However, more often than not, the level of detail required for making informed security decisions is missing from threat feeds, since most indicators are atomic in nature, like IPs and hashes, which are usually rather volatile. These feeds distinctly lack strategic threat information, like attack patterns and techniques that truly represent the behavior of an attacker or an exploit. Moreover, there is a lot of duplication in threat information and no single place where one could explore the entirety of a threat, hence requiring hundreds of man hours for sifting through numerous sources - trying to discern signal from noise - to find all the credible information on a threat. We have made use of natural language processing to extract threat feeds from unstructured cyber threat information sources with approximately 70\% precision, providing comprehensive threat reports in standards like STIX, which is a widely accepted industry standard that represents CTI. The automation of an otherwise tedious manual task would ensure the timely gathering and sharing of relevant CTI that would give organizations the edge to be able to proactively defend against known as well as unknown threats.</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -3850,9 +3986,21 @@
           <t>Cyber Threat Intelligence; Online dataset; Security Operations; CTI; Threat intelligence; AI</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Crossref search; OpenAlex search</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/fit.2018.00030</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3863,15 +4011,17 @@
           <t>Cyberattack Prediction Through Public Text  Analysis and Mini-Theories</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ian Perera; Jena D. Hwang; Kevin Bayas; Bonnie J. Dorr; Yorick Wilks</t>
+        </is>
       </c>
       <c r="D14" t="n">
         <v>2018</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>2018 IEEE International Conference on Big Data (Big Data)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3914,12 +4064,14 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>10.1109/bigdata.2018.8622106</t>
+        </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>venue normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref search; OpenAlex search; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -3939,7 +4091,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>This paper appears to address cyber attack prediction within the broader area of cyber threat intelligence. It likely focuses on detecting, classifying, or predicting security-relevant events or indicators from open or semi-open data sources. Relevant domains include Cyber Threat Intelligence; Cyber Risk Management; Security Operations; Intelligence Services; Government Services.</t>
+          <t>This paper describes a new approach to detection and tracking of potential cyberattacks from analyzing large quantities of cyber-related webpage text, using ontological knowledge about such attacks combined with composable causal models represented in Probabilistic Soft Logic. The stages of a cyberattack kill chain are viewed as a sequence of both observed and unobserved events (e.g., reconnaissance, weaponize, exploit, install) and explicit mentions of, or related to, such events are examined as potential signals for a future attack. Using a suite of natural language processing techniques, sentences from input news texts are automatically classified according to the described cyberattack event, then enriched with named entity recognition for the rapid detection of key elements that might be associated with potential cyberattacks. We present our work as a framework for rapid and flexible predictive analysis of the ever-increasing amount of cyber-related text data, with initial experiments indicating that event detection using parsing and named entity recognition combined with statistical relational learning show promise in time-series prediction from news text.</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -3947,9 +4099,21 @@
           <t>Cyber Attack Prediction; Online dataset; Cyber Threat Intelligence; Cyber Risk Management; Security Operations; Intelligence Services; Government Services; CTI</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Crossref search; OpenAlex search</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/bigdata.2018.8622106</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3960,15 +4124,17 @@
           <t>Acing the IOC Game: Toward Automatic Discovery and Analysis of Open Source Cyber Threat Intelligence</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Xiaojing Liao; Kan Yuan; XiaoFeng Wang; Zhou Li; Luyi Xing; Raheem Beyah</t>
+        </is>
       </c>
       <c r="D15" t="n">
         <v>2016</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Proceedings of the 2016 ACM SIGSAC Conference on Computer and Communications Security</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4018,7 +4184,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -4036,7 +4202,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>This paper appears to address cyber threat intelligence within the broader area of cyber threat intelligence. It likely contributes to threat intelligence collection, indicator extraction, or vulnerability-focused analysis using open-source data. Relevant domains include Cyber Threat Intelligence; Law Enforcement; Intelligence Services; Security Operations; Cyber Risk Management.</t>
+          <t>To adapt to the rapidly evolving landscape of cyber threats, security professionals are actively exchanging Indicators of Compromise (IOC) (e.g., malware signatures, botnet IPs) through public sources (e.g. blogs, forums, tweets, etc.). Such information, often presented in articles, posts, white papers etc., can be converted into a machine-readable OpenIOC format for automatic analysis and quick deployment to various security mechanisms like an intrusion detection system. With hundreds of thousands of sources in the wild, the IOC data are produced at a high volume and velocity today, which becomes increasingly hard to manage by humans. Efforts to automatically gather such information from unstructured text, however, is impeded by the limitations of today's Natural Language Processing (NLP) techniques, which cannot meet the high standard (in terms of accuracy and coverage) expected from the IOCs that could serve as direct input to a defense system. In this paper, we present iACE, an innovation solution for fully automated IOC extraction. Our approach is based upon the observation that the IOCs in technical articles are often described in a predictable way: being connected to a set of context terms (e.g., "download") through stable grammatical relations. Leveraging this observation, iACE is designed to automatically locate a putative IOC token (e.g., a zip file) and its context (e.g., "malware", "download") within the sentences in a technical article, and further analyze their relations through a novel application of graph mining techniques. Once the grammatical connection between the tokens is found to be in line with the way that the IOC is commonly presented, these tokens are extracted to generate an OpenIOC item that describes not only the indicator (e.g., a malicious zip file) but also its context (e.g., download from an external source). Running on 71,000 articles collected from 45 leading technical blogs, this new approach demonstrates a remarkable performance: it generated 900K OpenIOC items with a precision of 95% and a coverage over 90%, which is way beyond what the state-of-the-art NLP technique and industry IOC tool can achieve, at a speed of thousands of articles per hour. Further, by correlating the IOCs mined from the articles published over a 13-year span, our study sheds new light on the links across hundreds of seemingly unrelated attack instances, particularly their shared infrastructure resources, as well as the impacts of such open-source threat intelligence on security protection and evolution of attack strategies.</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -4044,9 +4210,21 @@
           <t>Cyber Threat Intelligence; Blogs; Law Enforcement; Intelligence Services; Security Operations; Cyber Risk Management; CTI; Threat intelligence</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/2976749.2978315</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4067,7 +4245,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ACM Digital Library</t>
+          <t>Digital Threats: Research and Practice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4117,7 +4295,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; publisher-native abstract; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -4135,7 +4313,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>This paper appears to address dark-web situational awareness / cti within the broader area of dark web &amp; underground sources. It likely contributes to threat intelligence collection, indicator extraction, or vulnerability-focused analysis using open-source data. Relevant domains include Cyber threat intelligence.</t>
+          <t>To increase situational awareness, major cybersecurity platforms offer Cyber Threat Intelligence (CTI) about emerging cyber threats, key threat actors, and their modus operandi. However, this intelligence is often reactive, as it analyzes event log files after attacks have already occurred, lacking more active scrutiny of potential threats brewing in cyberspace before an attack has occurred. One intelligence source receiving significant attention is the Dark Web, where significant quantities of malicious hacking tools and other cyber assets are hosted. We present the AZSecure Hacker Assets Portal (HAP). The Dark Web-based HAP collects, analyzes, and reports on the major Dark Web data sources to offer unique perspective of hackers, their cybercriminal assets, and their intentions and motivations, ultimately contributing CTI insights to improve situational awareness. HAP currently supports 200+ users internationally from academic institutions such as UT San Antonio and National Taiwan University, law enforcement entities such as Calgary and Ontario Provincial Police, and industry organizations including General Electric and PayPal.</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -4143,9 +4321,21 @@
           <t>Dark web; CTI; Hacker assets; Situational awareness; Cyber threat intelligence; Hacker forums; Threat intelligence; Dark Web Underground Sources; Dark-web situational awareness CTI</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>publisher-native abstract; OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3450972</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4156,15 +4346,17 @@
           <t>Threat Intelligence Generation Using Network Telescope Data for Industrial Control System</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Olivier Cabana; Amr M. Youssef; Mourad Debbabi; Bernard Lebel; Marthe Kassouf; Ribal Atallah; Basile L. Agba</t>
+        </is>
       </c>
       <c r="D17" t="n">
         <v>2021</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>IEEE Transactions on Information Forensics and Security</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4207,12 +4399,14 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>10.1109/tifs.2021.3078261</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>venue normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref search; OpenAlex search; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4230,7 +4424,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>This paper appears to address cyber threat intelligence within the broader area of dark web &amp; underground sources. It likely contributes to threat intelligence collection, indicator extraction, or vulnerability-focused analysis using open-source data. Relevant domains include Cyber Threat Inteligence; Security Operations.</t>
+          <t>Industrial Control Systems (ICSs) are cyber-physical systems that offer attractive targets to threat actors due to the scale of damages, both physical and cyber, that successful exploitation can cause. As such, ICSs often find themselves victims to reconnaissance campaigns - coordinated scanning activity that targets a wide subset of the Internet - that aim to discover vulnerable systems. As these campaigns likely scan broad netblocks of the Internet, some traffic is directed to network telescopes, which are routable, allocated, and unused IP space. In this paper, we explore the threat landscape of ICS devices by analyzing and investigating network telescope traffic. Our network traffic analysis tool takes darknet traffic and generates threat intelligence on scanning campaigns targeting ICSs in the form of campaign fragments, which we leverage in new ways to get more in-depth knowledge of the cybersecurity threats. We investigate the payloads of the identified campaigns using a custom Deep Packet Inspection (DPI) technique to dissect and analyze the packets. We found 13 distinct payload templates and deduced their purpose, and by extension the campaign goals. We use machine learning to classify the sources behind the campaigns and identify threat actors such as botnets, malicious attackers, or researchers, and establish a methodology to rank our campaigns to prioritize our analysis. To conduct our analysis of the threats targeting ICSs, we have leveraged 12.85 TB (330 days) of network traffic received by our observed darknet IP space. Combining these investigative threads, we provide a thorough overview of the threat landscape targeting ICS systems.</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -4238,9 +4432,21 @@
           <t>Cyber threat Intelligence; Dark Web; Onine dataset; Cyber Threat Inteligence; Security Operations; Threat intelligence; Network analysis; Dark Web Underground Sources</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Crossref search; OpenAlex search</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/tifs.2021.3078261</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4251,15 +4457,17 @@
           <t>Hacker Forum Exploit and Classification for Proactive Cyber Threat Intelligence</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apurv Singh Gautam; Yamini Gahlot; Pooja Kamat</t>
+        </is>
       </c>
       <c r="D18" t="n">
         <v>2020</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Springer</t>
+          <t>Lecture Notes in Networks and Systems</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4309,7 +4517,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4335,9 +4543,17 @@
           <t>Cyber Threat Intelligence; Forums; Security Operations; CTI; Threat intelligence; Dark Web Underground Sources</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/978-3-030-33846-6_32</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4358,7 +4574,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MDPI</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4408,7 +4624,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; publisher-native abstract; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -4426,7 +4642,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>This paper appears to address dark-web cti within the broader area of dark web &amp; underground sources. It likely focuses on detecting, classifying, or predicting security-relevant events or indicators from open or semi-open data sources. Relevant domains include Cyber threat intelligence; Security informatics.</t>
+          <t>Scientific work that leverages information about communities on the deep and dark web has opened up new angles in the field of security informatics. [...]</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -4434,9 +4650,21 @@
           <t>Dark web; CTI; Prediction; Security informatics; Cyber threat intelligence; Threat intelligence; Dark Web Underground Sources; Dark-web CTI</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>publisher-native abstract; OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/info9120305</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4449,7 +4677,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Humaira Arshad; Esther Omolara; Isaac Abiodun; Abdulhai Aminu</t>
+          <t>Humaira Arshad; Esther Omlara; Abiodun Esther Omolara; Abdullahi Aminu Kazaure</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4457,7 +4685,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Computers &amp;amp; Security</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4507,7 +4735,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4533,9 +4761,17 @@
           <t>Forensics; Social networks; Workflow; Investigation model; Digital forensics; Social media; Network analysis; Investigation workflow; Digital Forensics Evidence; Online social-network forensics workflow</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.cose.2020.101946</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4556,7 +4792,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Future Generation Computer Systems</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4606,7 +4842,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -4634,9 +4870,17 @@
           <t>Digital forensics; DFINT; OSINT fusion; Investigation; Mixed; OSINT; Digital Forensics Evidence; DFINT + OSINT integration</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.future.2016.12.032</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4657,7 +4901,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Springer</t>
+          <t>International Journal of Information Security</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4707,7 +4951,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex; publisher-native abstract; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -4727,7 +4971,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>This paper appears to address systematic review within the broader area of foundations &amp; reviews. It likely synthesizes prior literature, methods, and application areas, with particular relevance for analysts building OSINT-informed cyber investigation workflows. Relevant domains include General; Cyber threat intelligence.</t>
+          <t>Abstract This paper presents a systematic review to identify research combining artificial intelligence (AI) algorithms with Open source intelligence (OSINT) applications and practices. Currently, there is a lack of compilation of these approaches in the research domain and similar systematic reviews do not include research that post dates the year 2019. This systematic review attempts to fill this gap by identifying recent research. The review used the preferred reporting items for systematic reviews and meta-analyses and identified 163 research articles focusing on OSINT applications leveraging AI algorithms. This systematic review outlines several research questions concerning meta-analysis of the included research and seeks to identify research limitations and future directions in this area. The review identifies that research gaps exist in the following areas: Incorporation of pre-existing OSINT tools with AI, the creation of AI-based OSINT models that apply to penetration testing, underutilisation of alternate data sources and the incorporation of dissemination functionality. The review additionally identifies future research directions in AI-based OSINT research in the following areas: Multi-lingual support, incorporation of additional data sources, improved model robustness against data poisoning, integration with live applications, real-world use, the addition of alert generation for dissemination purposes and incorporation of algorithms for use in planning.</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -4735,9 +4979,21 @@
           <t>Systematic review; AI for OSINT; Taxonomy; General; Cyber threat intelligence; Mixed; OSINT; AI; Foundations Reviews</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>publisher-native abstract; OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10207-024-00868-2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4758,7 +5014,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Springer</t>
+          <t>Artificial Intelligence Review</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4808,7 +5064,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4834,9 +5090,17 @@
           <t>Review; Cyber security; Digital forensics; Cybercrime; Web archives; Social media; Public records; Code repositories; CTI; Foundations Reviews</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s10462-023-10454-y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4857,7 +5121,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Computers in Human Behavior</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4907,7 +5171,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4933,9 +5197,17 @@
           <t>OSINT theory; Foundations; Internet-age intelligence; General; General web sources; OSINT; Foundations Reviews; OSINT theory foundational review</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.chb.2011.11.014</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4946,15 +5218,17 @@
           <t>Resolving cross-site scripting attacks through genetic algorithm and reinforcement learning</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Iram Tariq; Muddassar Azam Sindhu; Rabeeh Ayaz Abbasi; Akmal Saeed Khattak; Onaiza Maqbool; Ghazanfar Farooq Siddiqui</t>
+        </is>
       </c>
       <c r="D25" t="n">
         <v>2021</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elsevier / ScienceDirect</t>
+          <t>Expert Systems with Applications</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5004,7 +5278,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>venue+doi normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue+doi normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref; OpenAlex</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -5030,9 +5304,17 @@
           <t>Cross Site Scripting Detection; Online dataset; Security Operations; Cyber Threat Intelligence; Malicious infrastructure; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Crossref; OpenAlex</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.eswa.2020.114386</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5043,15 +5325,17 @@
           <t>A Visualized Botnet Detection System Based Deep Learning for the Internet of Things Networks of Smart Cities</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>R. Vinayakumar; Mamoun Alazab; Sriram Srinivasan; Quoc-Viet Pham; Soman Kotti Padannayil; K. Simran</t>
+        </is>
       </c>
       <c r="D26" t="n">
         <v>2020</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IEEE</t>
+          <t>IEEE Transactions on Industry Applications</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5094,12 +5378,14 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>10.1109/tia.2020.2971952</t>
+        </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>venue normalized; Generated synopsis; Keyword enriched</t>
+          <t>venue normalized; Generated synopsis; Keyword enriched; Authoritative harvest: Crossref search; OpenAlex search; OpenAlex abstract</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -5117,7 +5403,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>This paper appears to address botnet detection within the broader area of malicious infrastructure &amp; exploit discovery. It likely focuses on detecting, classifying, or predicting security-relevant events or indicators from open or semi-open data sources. Relevant domains include Cyber Threat Intelligence; Security Operations.</t>
+          <t>Internet of Things applications for smart cities have currently become a primary target for advanced persistent threats of botnets. This article proposes a botnet detection system based on a two-level deep learning framework for semantically discriminating botnets and legitimate behaviors at the application layer of the domain name system (DNS) services. In the first level of the framework, the similarity measures of DNS queries are estimated using siamese networks based on a predefined threshold for selecting the most frequent DNS information across Ethernet connections. In the second level of the framework, a domain generation algorithm based on deep learning architectures is suggested for categorizing normal and abnormal domain names. The framework is highly scalable on a commodity hardware server due to its potential design of analyzing DNS data. The proposed framework was evaluated using two datasets and was compared with recent deep learning models. Various visualization methods were also employed to understand the characteristics of the dataset and to visualize the embedding features. The experimental results revealed substantial improvements in terms of F1-score, speed of detection, and false alarm rate.</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -5125,9 +5411,21 @@
           <t>Botnet Detection; Domain Name Generation Algorithm Detection; Online dataset; Cyber Threat Intelligence; Security Operations; CTI; Network analysis; AI; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Crossref search; OpenAlex search</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>OpenAlex abstract</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/tia.2020.2971952</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5222,9 +5520,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Domain Name System; Security Operations; Cyber Threat Intelligence; CTI; Malware; Malicious infrastructure; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v/>
+      </c>
+      <c r="V27" t="n">
+        <v/>
+      </c>
+      <c r="W27" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5319,9 +5623,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v/>
+      </c>
+      <c r="V28" t="n">
+        <v/>
+      </c>
+      <c r="W28" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5416,9 +5726,15 @@
           <t>Domain Name Generation Algorithm Detection; Online Dataset; Domain Name System; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; Network analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v/>
+      </c>
+      <c r="V29" t="n">
+        <v/>
+      </c>
+      <c r="W29" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5513,9 +5829,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; Network analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v/>
+      </c>
+      <c r="V30" t="n">
+        <v/>
+      </c>
+      <c r="W30" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5610,9 +5932,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; Network analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v/>
+      </c>
+      <c r="V31" t="n">
+        <v/>
+      </c>
+      <c r="W31" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5705,9 +6033,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Domain Name Service; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; AI; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v/>
+      </c>
+      <c r="V32" t="n">
+        <v/>
+      </c>
+      <c r="W32" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5800,9 +6134,15 @@
           <t>Malicious Domain Name Detection; Online dataset; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; Network analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v/>
+      </c>
+      <c r="V33" t="n">
+        <v/>
+      </c>
+      <c r="W33" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5897,9 +6237,15 @@
           <t>Malicious Domain detection; Domain Name Generation Algorithm Detection; Online Dataset; Cyber threat intelligence; Security operations; Malicious infrastructure; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v/>
+      </c>
+      <c r="V34" t="n">
+        <v/>
+      </c>
+      <c r="W34" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5992,9 +6338,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Domain Name System; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; AI; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v/>
+      </c>
+      <c r="V35" t="n">
+        <v/>
+      </c>
+      <c r="W35" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6089,9 +6441,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Security Operations; Cyber Threat Intelligence; CTI; Malicious infrastructure; AI; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v/>
+      </c>
+      <c r="V36" t="n">
+        <v/>
+      </c>
+      <c r="W36" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -6186,9 +6544,15 @@
           <t>Malicious URL Detection; Online Dataset; Cyber Threat intelligence; Security Operations; Cyber Risk management; Malicious infrastructure; AI; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="U37" t="n">
+        <v/>
+      </c>
+      <c r="V37" t="n">
+        <v/>
+      </c>
+      <c r="W37" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -6281,9 +6645,15 @@
           <t>Domain Name Generation Algorithm Detection; Malicious URL Detection; Online dataset; Security Operations; Cyber Threat Intelligence; CTI; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v/>
+      </c>
+      <c r="V38" t="n">
+        <v/>
+      </c>
+      <c r="W38" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -6376,9 +6746,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Security Operations; Cyber Threat Intelligence; CTI; Malware; Malicious infrastructure; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="U39" t="n">
+        <v/>
+      </c>
+      <c r="V39" t="n">
+        <v/>
+      </c>
+      <c r="W39" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6469,9 +6845,15 @@
           <t>Phishing URL Classification; Online Dataset; Cyber Threat Inteligence; Security Operations; Phishing; Malicious infrastructure; Network analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v/>
+      </c>
+      <c r="V40" t="n">
+        <v/>
+      </c>
+      <c r="W40" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6566,9 +6948,15 @@
           <t>Cyber Threat Intelligence; Social Media; Blogs; Security Reports; Security Operations; CTI; Threat intelligence; Network analysis; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v/>
+      </c>
+      <c r="V41" t="n">
+        <v/>
+      </c>
+      <c r="W41" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6663,9 +7051,15 @@
           <t>Cyber Threat Intelligence; Social Media; Law Enforcement; Intelligence Services; Security Operations; Cyber Risk Management; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="U42" t="n">
+        <v/>
+      </c>
+      <c r="V42" t="n">
+        <v/>
+      </c>
+      <c r="W42" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6760,9 +7154,15 @@
           <t>Cyber Threat Intelligence; Websites; Social Media; Online Forums; Law Enforcement; Intelligence Services; Security Operations; Cyber Risk Management; Threat intelligence; AI</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="U43" t="n">
+        <v/>
+      </c>
+      <c r="V43" t="n">
+        <v/>
+      </c>
+      <c r="W43" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6857,9 +7257,15 @@
           <t>Cyber Threat Intelligence; Social Media; Online dataset; Security Operations; Intelligence Services; Goverment Departments; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v/>
+      </c>
+      <c r="V44" t="n">
+        <v/>
+      </c>
+      <c r="W44" t="n">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6954,9 +7360,15 @@
           <t>Cyber Threat Intelligence; Social Media; Online News; Security Operations; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v/>
+      </c>
+      <c r="V45" t="n">
+        <v/>
+      </c>
+      <c r="W45" t="n">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -7051,9 +7463,15 @@
           <t>Cyber Threat Intelligence; Social Media; Security Operations; AI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v/>
+      </c>
+      <c r="V46" t="n">
+        <v/>
+      </c>
+      <c r="W46" t="n">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7148,9 +7566,15 @@
           <t>Cyber Threat Intelligence; Online Dataset; Social Media; Online news; Security Operations; Threat intelligence; AI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v/>
+      </c>
+      <c r="V47" t="n">
+        <v/>
+      </c>
+      <c r="W47" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7245,9 +7669,15 @@
           <t>Cyber Threat Intelligence; Social Media; Security Operations; CTI; Threat intelligence; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v/>
+      </c>
+      <c r="V48" t="n">
+        <v/>
+      </c>
+      <c r="W48" t="n">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7340,9 +7770,15 @@
           <t>Cyber Threat Intelligence; Social Media; Security Operations; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v/>
+      </c>
+      <c r="V49" t="n">
+        <v/>
+      </c>
+      <c r="W49" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7435,9 +7871,15 @@
           <t>Cyber Threat Intelligence; Online dataset; Blogs; Social Media; Security Operations; Intelligence Services; Goverment Departments; Threat intelligence; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v/>
+      </c>
+      <c r="V50" t="n">
+        <v/>
+      </c>
+      <c r="W50" t="n">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7530,9 +7972,15 @@
           <t>Cyber Threat Intelligence; Social Media; Security Operations; CTI; Network analysis; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v/>
+      </c>
+      <c r="V51" t="n">
+        <v/>
+      </c>
+      <c r="W51" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7625,9 +8073,15 @@
           <t>DDoS attack prediction; Social Media; Cyber Risk management; Security Operations; Cyber Threat Intelligence; CTI; AI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="U52" t="n">
+        <v/>
+      </c>
+      <c r="V52" t="n">
+        <v/>
+      </c>
+      <c r="W52" t="n">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7722,9 +8176,15 @@
           <t>Cyber Threat Intelligence; Social Media; Security Operations; Intelligence Services; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="U53" t="n">
+        <v/>
+      </c>
+      <c r="V53" t="n">
+        <v/>
+      </c>
+      <c r="W53" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7819,9 +8279,15 @@
           <t>Cyber Threat Intelligence; Social Media; Online dataset; Security Operations; CTI; Threat intelligence; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="U54" t="n">
+        <v/>
+      </c>
+      <c r="V54" t="n">
+        <v/>
+      </c>
+      <c r="W54" t="n">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7916,9 +8382,15 @@
           <t>Threat Intelligence Posioning Prevention; Social Media; Cyber Threat Intelligence; Security Operations; Threat intelligence; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="U55" t="n">
+        <v/>
+      </c>
+      <c r="V55" t="n">
+        <v/>
+      </c>
+      <c r="W55" t="n">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8013,9 +8485,15 @@
           <t>Cyber Threat Intelligence; Social Media; Security Operations; CTI; AI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="U56" t="n">
+        <v/>
+      </c>
+      <c r="V56" t="n">
+        <v/>
+      </c>
+      <c r="W56" t="n">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8112,9 +8590,15 @@
           <t>Social media; Cybercrime; Mitigation; OSINT; Threat analysis; Social Media OSINT Collection; Cybercrime mitigation social-media OSINT</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="U57" t="n">
+        <v/>
+      </c>
+      <c r="V57" t="n">
+        <v/>
+      </c>
+      <c r="W57" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8209,9 +8693,15 @@
           <t>Cyber Attack Detection; Search Engine; Social Media; Security Operations; Cyber Threat Intelligence; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="U58" t="n">
+        <v/>
+      </c>
+      <c r="V58" t="n">
+        <v/>
+      </c>
+      <c r="W58" t="n">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8306,9 +8796,15 @@
           <t>Spam Detection; Social Media; Cyber Threat Intelligence; Security Operations; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="U59" t="n">
+        <v/>
+      </c>
+      <c r="V59" t="n">
+        <v/>
+      </c>
+      <c r="W59" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8403,9 +8899,15 @@
           <t>Cyber Attack Prediction; Social Media; Online Dataset; Onlline News; Cyber Threat Intelligence; Security Operations; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v/>
+      </c>
+      <c r="V60" t="n">
+        <v/>
+      </c>
+      <c r="W60" t="n">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8502,9 +9004,15 @@
           <t>Vulnerability assessment; AI augmentation; Workflow; Small business; Small-business cybersecurity; Public web data; OSINT; Vulnerability analysis; Investigation workflow; Vulnerability Discovery Attack Surface</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v/>
+      </c>
+      <c r="V61" t="n">
+        <v/>
+      </c>
+      <c r="W61" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8597,9 +9105,15 @@
           <t>Cyber Vulnerability Detection; Online News; Cyber Threat Intelligence; Security Operations; CTI; AI; Vulnerability Discovery Attack Surface</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v/>
+      </c>
+      <c r="V62" t="n">
+        <v/>
+      </c>
+      <c r="W62" t="n">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8690,9 +9204,15 @@
           <t>Cyber Vulnerability Detection; Social Media; Security Operations; Cyber Threat Intelligence; Cyber Risk management; CTI; Vulnerability analysis; Vulnerability Discovery Attack Surface</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="U63" t="n">
+        <v/>
+      </c>
+      <c r="V63" t="n">
+        <v/>
+      </c>
+      <c r="W63" t="n">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8785,9 +9305,15 @@
           <t>Fake Cyber Intelligence Generation; Online dataset; CVE records; Intelligence Services; Defense; Penetration Testing; CTI; Threat intelligence; Cyber Threat Intelligence</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="U64" t="n">
+        <v/>
+      </c>
+      <c r="V64" t="n">
+        <v/>
+      </c>
+      <c r="W64" t="n">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8882,9 +9408,15 @@
           <t>Knowledge Graph Improvement; Blogs; Online dataset; Security Operations; CTI; AI; Cyber Threat Intelligence</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="U65" t="n">
+        <v/>
+      </c>
+      <c r="V65" t="n">
+        <v/>
+      </c>
+      <c r="W65" t="n">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8979,9 +9511,15 @@
           <t>Dark Web Monitoring; Dark Web; Dark Web Market Places; Cyber Threat Intelligence; Dark Web Underground Sources</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="U66" t="n">
+        <v/>
+      </c>
+      <c r="V66" t="n">
+        <v/>
+      </c>
+      <c r="W66" t="n">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9076,9 +9614,15 @@
           <t>Cyber Threat Intelligence; Dark Web; Domain Name System; Investigation workflow; Dark Web Underground Sources</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="U67" t="n">
+        <v/>
+      </c>
+      <c r="V67" t="n">
+        <v/>
+      </c>
+      <c r="W67" t="n">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9175,9 +9719,15 @@
           <t>Review; Cybersecurity; OPSEC; Tools and methods; Mixed; OSINT; Foundations Reviews</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
+      <c r="U68" t="n">
+        <v/>
+      </c>
+      <c r="V68" t="n">
+        <v/>
+      </c>
+      <c r="W68" t="n">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9274,9 +9824,15 @@
           <t>Workflow; Collaboration; Scaling investigations; Crowdsourcing; Investigations; HCI; Mixed public sources; OSINT; Investigation workflow; Investigative Workflows Collaboration</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="U69" t="n">
+        <v/>
+      </c>
+      <c r="V69" t="n">
+        <v/>
+      </c>
+      <c r="W69" t="n">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9371,9 +9927,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Security Operations; CTI; Malicious infrastructure; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
+      <c r="U70" t="n">
+        <v/>
+      </c>
+      <c r="V70" t="n">
+        <v/>
+      </c>
+      <c r="W70" t="n">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9468,9 +10030,15 @@
           <t>Phishing Classification; Online dataset; Domain Name System; Security Blogs; Security Operations; Law Enforcement; Phishing; Malicious infrastructure; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="U71" t="n">
+        <v/>
+      </c>
+      <c r="V71" t="n">
+        <v/>
+      </c>
+      <c r="W71" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9561,9 +10129,15 @@
           <t>Vulnerability Detection; Online dataset; Security Operations; CTI; Vulnerability analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="U72" t="n">
+        <v/>
+      </c>
+      <c r="V72" t="n">
+        <v/>
+      </c>
+      <c r="W72" t="n">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9658,9 +10232,15 @@
           <t>Domain Name Generation Algorithm Detection; Online dataset; Security Operations; CTI; Malicious infrastructure; Network analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
+      <c r="U73" t="n">
+        <v/>
+      </c>
+      <c r="V73" t="n">
+        <v/>
+      </c>
+      <c r="W73" t="n">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9755,9 +10335,15 @@
           <t>Malware Detection; Online dataset; Security Operations; CTI; Malware; Network analysis; Malicious Infrastructure Exploit Discovery</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="U74" t="n">
+        <v/>
+      </c>
+      <c r="V74" t="n">
+        <v/>
+      </c>
+      <c r="W74" t="n">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9850,9 +10436,15 @@
           <t>Malicious Email Campaign Prediction; Online dataset; Online Forums; Security Operations; Law Enforcement; Intelligence Services; Goverment Departments; Defence; Other</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
+      <c r="U75" t="n">
+        <v/>
+      </c>
+      <c r="V75" t="n">
+        <v/>
+      </c>
+      <c r="W75" t="n">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9947,9 +10539,15 @@
           <t>Cyber Security Event Detection; Social Media; Security Operations; Incident Response; OSINT; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="U76" t="n">
+        <v/>
+      </c>
+      <c r="V76" t="n">
+        <v/>
+      </c>
+      <c r="W76" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10040,9 +10638,15 @@
           <t>Social Media Account Classification; Social Media; Online Dataset; Cyber threat intelligence; Law Enforcement; Intelligence Services; Penetration Testing; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="U77" t="n">
+        <v/>
+      </c>
+      <c r="V77" t="n">
+        <v/>
+      </c>
+      <c r="W77" t="n">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10137,9 +10741,15 @@
           <t>Sensitive Data Disclosure Analysis; Social Media; Security Operations; Defence; Goverment Departments; Intelligence Services; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="U78" t="n">
+        <v/>
+      </c>
+      <c r="V78" t="n">
+        <v/>
+      </c>
+      <c r="W78" t="n">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10232,9 +10842,15 @@
           <t>Cyber Attack Prediction; Social Media; Security Operations; Intelligence Services; Goverment Departments; Law Enforcement; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="U79" t="n">
+        <v/>
+      </c>
+      <c r="V79" t="n">
+        <v/>
+      </c>
+      <c r="W79" t="n">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10325,9 +10941,15 @@
           <t>OSINT Investigations; Social Media; Intelligence Services; Law Enforcement; Penetration Testing; OSINT; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
+      <c r="U80" t="n">
+        <v/>
+      </c>
+      <c r="V80" t="n">
+        <v/>
+      </c>
+      <c r="W80" t="n">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10424,9 +11046,15 @@
           <t>Cyber Attack Prediction; Social Media; Security Operations; Intelligence Services; Goverment Departments; Law Enforcement; CTI; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="U81" t="n">
+        <v/>
+      </c>
+      <c r="V81" t="n">
+        <v/>
+      </c>
+      <c r="W81" t="n">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10521,9 +11149,15 @@
           <t>Text Analysis; Sentiment Analysis; Social Media; Onliune Forum Posts; Online dataset; Intelligence Services; Government Departments; Security Operations; Law Enforcement; Social Media OSINT Collection</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="U82" t="n">
+        <v/>
+      </c>
+      <c r="V82" t="n">
+        <v/>
+      </c>
+      <c r="W82" t="n">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10614,9 +11248,15 @@
           <t>Malicious IP forcasting; Online dataset; Paste Sites; Social Media; Threat Intelligence; Law Enforcement; Cyber Risk Management; Security Operations; CTI; AI</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="U83" t="n">
+        <v/>
+      </c>
+      <c r="V83" t="n">
+        <v/>
+      </c>
+      <c r="W83" t="n">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10713,9 +11353,15 @@
           <t>Real-time detection; Framework; OSINT tools; Cyber threats; Cyber threat detection; Open-source tools; Mixed public sources; CTI; Threat Detection Prediction; Real-time OSINT threat-detection framework</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="U84" t="n">
+        <v/>
+      </c>
+      <c r="V84" t="n">
+        <v/>
+      </c>
+      <c r="W84" t="n">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10808,9 +11454,15 @@
           <t>Cyber Attack Detection; Online dataset; Security Operations; CTI; Network analysis; AI; Threat Detection Prediction</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="U85" t="n">
+        <v/>
+      </c>
+      <c r="V85" t="n">
+        <v/>
+      </c>
+      <c r="W85" t="n">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10905,9 +11557,15 @@
           <t>Cyber Attack Detection; Online dataset; Security Operations; CTI; Threat Detection Prediction</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="U86" t="n">
+        <v/>
+      </c>
+      <c r="V86" t="n">
+        <v/>
+      </c>
+      <c r="W86" t="n">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10998,9 +11656,15 @@
           <t>Intrusion Detection System; Online dataset; Security Operations; CTI; AI; Threat Detection Prediction</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="U87" t="n">
+        <v/>
+      </c>
+      <c r="V87" t="n">
+        <v/>
+      </c>
+      <c r="W87" t="n">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11093,9 +11757,15 @@
           <t>Port Scanning Defence; Online dataset; Security Operations; Network analysis; AI; Threat Detection Prediction</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="U88" t="n">
+        <v/>
+      </c>
+      <c r="V88" t="n">
+        <v/>
+      </c>
+      <c r="W88" t="n">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11190,9 +11860,15 @@
           <t>Fuzzing Identification; Online dataset; Security Operations; AI; Vulnerability Discovery Attack Surface</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="U89" t="n">
+        <v/>
+      </c>
+      <c r="V89" t="n">
+        <v/>
+      </c>
+      <c r="W89" t="n">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11287,9 +11963,15 @@
           <t>Vulnerabiltiy Exploitation Probablity; Online dataset; Security Operations; Cyber Risk Management; CTI; Vulnerability analysis; AI; Vulnerability Discovery Attack Surface</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
+      <c r="U90" t="n">
+        <v/>
+      </c>
+      <c r="V90" t="n">
+        <v/>
+      </c>
+      <c r="W90" t="n">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11382,9 +12064,15 @@
           <t>Cyber Reconnaissance Detection; Online dataset; Security Operations; CTI; AI; Vulnerability Discovery Attack Surface</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
+      <c r="U91" t="n">
+        <v/>
+      </c>
+      <c r="V91" t="n">
+        <v/>
+      </c>
+      <c r="W91" t="n">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11477,9 +12165,15 @@
           <t>Cyber threat intelligence; Misinformation; Intelligence Services; Law Enforcement; Non-Goverment Organisations; Goverment Departments; Online dataset; Online news; CTI; AI</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
+      <c r="U92" t="n">
+        <v/>
+      </c>
+      <c r="V92" t="n">
+        <v/>
+      </c>
+      <c r="W92" t="n">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11572,9 +12266,15 @@
           <t>Cyber threat intelligence; Vulnerability detection; Social media; Seucrity Operations; Intelligence Services; CTI</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
+      <c r="U93" t="n">
+        <v/>
+      </c>
+      <c r="V93" t="n">
+        <v/>
+      </c>
+      <c r="W93" t="n">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11669,9 +12369,15 @@
           <t>Social media; Intelligence Services; Law Enforcement; AI; Threat Detection Prediction; SOCMINT</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
+      <c r="U94" t="n">
+        <v/>
+      </c>
+      <c r="V94" t="n">
+        <v/>
+      </c>
+      <c r="W94" t="n">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11760,9 +12466,15 @@
           <t>Social media; General; AI; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+      <c r="U95" t="n">
+        <v/>
+      </c>
+      <c r="V95" t="n">
+        <v/>
+      </c>
+      <c r="W95" t="n">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11857,9 +12569,15 @@
           <t>Cyber threat intelligence; Social media; Misinformation; Intelligence Services; Law Enforcement; Non-Goverment Organisations; Goverment Departments; Online News; CTI</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
+      <c r="U96" t="n">
+        <v/>
+      </c>
+      <c r="V96" t="n">
+        <v/>
+      </c>
+      <c r="W96" t="n">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11950,9 +12668,15 @@
           <t>OSINT; Cyber threat intelligence; Social media; Intelligence Services; Law Enforcement; Penetration Testing; CTI</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
+      <c r="U97" t="n">
+        <v/>
+      </c>
+      <c r="V97" t="n">
+        <v/>
+      </c>
+      <c r="W97" t="n">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12043,9 +12767,15 @@
           <t>OSINT; Cyber threat intelligence; Dark web; Illicit markets; Intelligence Services; Law Enforcement; Non-Goverment Organisations; Goverment Departments; Online News; CTI</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
+      <c r="U98" t="n">
+        <v/>
+      </c>
+      <c r="V98" t="n">
+        <v/>
+      </c>
+      <c r="W98" t="n">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12142,9 +12872,15 @@
           <t>Cyber threat intelligence; Social media; Security Operations; Intelligence Services; Goverment Departments; Law Enforcement; CTI</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
+      <c r="U99" t="n">
+        <v/>
+      </c>
+      <c r="V99" t="n">
+        <v/>
+      </c>
+      <c r="W99" t="n">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12233,9 +12969,15 @@
           <t>OSINT; Cyber threat intelligence; Social media; Intelligence Services; Law Enforcement; Penetration Testing; CTI; Threat intelligence</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
+      <c r="U100" t="n">
+        <v/>
+      </c>
+      <c r="V100" t="n">
+        <v/>
+      </c>
+      <c r="W100" t="n">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12330,9 +13072,15 @@
           <t>OSINT; Social media; Intelligence Services; Law Enforcement; Penetration Testing; Malicious infrastructure; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
+      <c r="U101" t="n">
+        <v/>
+      </c>
+      <c r="V101" t="n">
+        <v/>
+      </c>
+      <c r="W101" t="n">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12425,9 +13173,15 @@
           <t>Cyber threat intelligence; Social media; Cyber harassment; Law enforcement; CTI</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
+      <c r="U102" t="n">
+        <v/>
+      </c>
+      <c r="V102" t="n">
+        <v/>
+      </c>
+      <c r="W102" t="n">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12522,9 +13276,15 @@
           <t>OSINT; Cyber threat intelligence; Social media; Misinformation; Goverment Departments; Public Health; Intelligence Services; Online News; CTI</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
+      <c r="U103" t="n">
+        <v/>
+      </c>
+      <c r="V103" t="n">
+        <v/>
+      </c>
+      <c r="W103" t="n">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12619,9 +13379,15 @@
           <t>Social media; Network analysis; General; Investigative Workflows Collaboration; Other</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
+      <c r="U104" t="n">
+        <v/>
+      </c>
+      <c r="V104" t="n">
+        <v/>
+      </c>
+      <c r="W104" t="n">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12714,9 +13480,15 @@
           <t>Cyber threat intelligence; Social media; Law Enforcement; Emergency Services; CTI</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
+      <c r="U105" t="n">
+        <v/>
+      </c>
+      <c r="V105" t="n">
+        <v/>
+      </c>
+      <c r="W105" t="n">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12811,9 +13583,15 @@
           <t>Cyber threat intelligence; General; Online News; CTI</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
+      <c r="U106" t="n">
+        <v/>
+      </c>
+      <c r="V106" t="n">
+        <v/>
+      </c>
+      <c r="W106" t="n">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12908,9 +13686,15 @@
           <t>Social media; Law enforcement; Intelligence Services; AI; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
+      <c r="U107" t="n">
+        <v/>
+      </c>
+      <c r="V107" t="n">
+        <v/>
+      </c>
+      <c r="W107" t="n">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13003,9 +13787,15 @@
           <t>Social media; General; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
+      <c r="U108" t="n">
+        <v/>
+      </c>
+      <c r="V108" t="n">
+        <v/>
+      </c>
+      <c r="W108" t="n">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13100,9 +13890,15 @@
           <t>Social media; Intelligence Services; Non-Goverment Organisations; Goverment Departments; Law Enforcement; Web Pages; Web Feeds; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
+      <c r="U109" t="n">
+        <v/>
+      </c>
+      <c r="V109" t="n">
+        <v/>
+      </c>
+      <c r="W109" t="n">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13197,9 +13993,15 @@
           <t>Social media; General; AI; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
+      <c r="U110" t="n">
+        <v/>
+      </c>
+      <c r="V110" t="n">
+        <v/>
+      </c>
+      <c r="W110" t="n">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13292,9 +14094,15 @@
           <t>OSINT; Cyber threat intelligence; Misinformation; Intelligence Services; Goverment Departments; Law Enforcement; Online dataset; News Articles; CTI</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
+      <c r="U111" t="n">
+        <v/>
+      </c>
+      <c r="V111" t="n">
+        <v/>
+      </c>
+      <c r="W111" t="n">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13387,9 +14195,15 @@
           <t>Cyber threat intelligence; Social media; Cyber harassment; Network analysis; Intelligence Services; Law Enforcement; Non-Goverment Organisations; CTI; AI</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
+      <c r="U112" t="n">
+        <v/>
+      </c>
+      <c r="V112" t="n">
+        <v/>
+      </c>
+      <c r="W112" t="n">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13484,9 +14298,15 @@
           <t>Cyber threat intelligence; Social media; Law enforcement; Non-Goverment Organisations; Online dataset; CTI; Network analysis</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
+      <c r="U113" t="n">
+        <v/>
+      </c>
+      <c r="V113" t="n">
+        <v/>
+      </c>
+      <c r="W113" t="n">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13581,9 +14401,15 @@
           <t>Social media; Hate speech; Law enforcement; Intelligence Services; Non-Goverment Organisations; Goverment Departments; Threat Detection Prediction; SOCMINT</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
+      <c r="U114" t="n">
+        <v/>
+      </c>
+      <c r="V114" t="n">
+        <v/>
+      </c>
+      <c r="W114" t="n">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13678,9 +14504,15 @@
           <t>OSINT; Law enforcement; Intelligence Services; Penetration Testing; Not Specified; Investigation workflow; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
+      <c r="U115" t="n">
+        <v/>
+      </c>
+      <c r="V115" t="n">
+        <v/>
+      </c>
+      <c r="W115" t="n">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13771,9 +14603,15 @@
           <t>Social media; Law enforcement; Intelligence Services; AI; Threat Detection Prediction; SOCMINT</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
+      <c r="U116" t="n">
+        <v/>
+      </c>
+      <c r="V116" t="n">
+        <v/>
+      </c>
+      <c r="W116" t="n">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13862,9 +14700,15 @@
           <t>Cyber threat intelligence; Social media; Hate speech; Law enforcement; Intelligence Services; Goverment Departments; Non-Goverment Organisations; CTI; AI</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
+      <c r="U117" t="n">
+        <v/>
+      </c>
+      <c r="V117" t="n">
+        <v/>
+      </c>
+      <c r="W117" t="n">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13955,9 +14799,15 @@
           <t>Cyber threat intelligence; Misinformation; Online News; Online dataset; CTI; AI</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="U118" t="n">
+        <v/>
+      </c>
+      <c r="V118" t="n">
+        <v/>
+      </c>
+      <c r="W118" t="n">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14046,9 +14896,15 @@
           <t>Social media; General; Online dataset; Network analysis; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
+      <c r="U119" t="n">
+        <v/>
+      </c>
+      <c r="V119" t="n">
+        <v/>
+      </c>
+      <c r="W119" t="n">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14141,9 +14997,15 @@
           <t>Social media; Intelligence Services; Law Enforcement; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
+      <c r="U120" t="n">
+        <v/>
+      </c>
+      <c r="V120" t="n">
+        <v/>
+      </c>
+      <c r="W120" t="n">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14238,9 +15100,15 @@
           <t>Cyber threat intelligence; Social media; Intelligence Services; Law Enforcement; RSS Feeds; Online Maps; Online Directories; CTI</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
+      <c r="U121" t="n">
+        <v/>
+      </c>
+      <c r="V121" t="n">
+        <v/>
+      </c>
+      <c r="W121" t="n">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14333,9 +15201,15 @@
           <t>OSINT; Intelligence Services; Law Enforcement; Websites; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
+      <c r="U122" t="n">
+        <v/>
+      </c>
+      <c r="V122" t="n">
+        <v/>
+      </c>
+      <c r="W122" t="n">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14426,9 +15300,15 @@
           <t>Cyber threat intelligence; General; CTI</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
+      <c r="U123" t="n">
+        <v/>
+      </c>
+      <c r="V123" t="n">
+        <v/>
+      </c>
+      <c r="W123" t="n">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14517,9 +15397,15 @@
           <t>Cyber threat intelligence; Malicious infrastructure; Security Operations; Online dataset; CTI</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
+      <c r="U124" t="n">
+        <v/>
+      </c>
+      <c r="V124" t="n">
+        <v/>
+      </c>
+      <c r="W124" t="n">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14614,9 +15500,15 @@
           <t>Reconnaissance; Defence; Intelligence Services; Online dataset; Network analysis; Malicious Infrastructure Exploit Discovery; Other</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
+      <c r="U125" t="n">
+        <v/>
+      </c>
+      <c r="V125" t="n">
+        <v/>
+      </c>
+      <c r="W125" t="n">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14705,9 +15597,15 @@
           <t>Social media; General; Foundations Reviews; SOCMINT</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
+      <c r="U126" t="n">
+        <v/>
+      </c>
+      <c r="V126" t="n">
+        <v/>
+      </c>
+      <c r="W126" t="n">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14802,9 +15700,15 @@
           <t>Cyber threat intelligence; Social media; Geolocation; Image; Intelligence Services; Law Enforcement; CTI</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
+      <c r="U127" t="n">
+        <v/>
+      </c>
+      <c r="V127" t="n">
+        <v/>
+      </c>
+      <c r="W127" t="n">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14893,9 +15797,15 @@
           <t>Cyber threat intelligence; Social media; Dark web; Illicit markets; Digital forensics; Law Enforcement; Public Health; AI; CTI</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
+      <c r="U128" t="n">
+        <v/>
+      </c>
+      <c r="V128" t="n">
+        <v/>
+      </c>
+      <c r="W128" t="n">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14990,9 +15900,15 @@
           <t>Social media; Geolocation; Image; Law Enforcement; Intelligence Services; Investigative Workflows Collaboration; SOCMINT</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
+      <c r="U129" t="n">
+        <v/>
+      </c>
+      <c r="V129" t="n">
+        <v/>
+      </c>
+      <c r="W129" t="n">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15085,9 +16001,15 @@
           <t>Social media; Public Health; Goverment Departments; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr"/>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
+      <c r="U130" t="n">
+        <v/>
+      </c>
+      <c r="V130" t="n">
+        <v/>
+      </c>
+      <c r="W130" t="n">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15178,9 +16100,15 @@
           <t>Social media; Law Enforcement; Intelligence Services; Goverment Departments; Non-Goverment Organisations; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
+      <c r="U131" t="n">
+        <v/>
+      </c>
+      <c r="V131" t="n">
+        <v/>
+      </c>
+      <c r="W131" t="n">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15275,9 +16203,15 @@
           <t>OSINT; Social media; Dark web; Illicit markets; Intelligence Services; Law Enforcement; Penetration Testing; Online Forums; Dark Web Underground Sources; SOCMINT</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr"/>
-      <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
+      <c r="U132" t="n">
+        <v/>
+      </c>
+      <c r="V132" t="n">
+        <v/>
+      </c>
+      <c r="W132" t="n">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15370,9 +16304,15 @@
           <t>Cyber threat intelligence; Social media; Misinformation; Intelligence Services; Law Enforcement; Non-Goverment Organisations; Goverment Departments; AI; CTI</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
+      <c r="U133" t="n">
+        <v/>
+      </c>
+      <c r="V133" t="n">
+        <v/>
+      </c>
+      <c r="W133" t="n">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15465,9 +16405,15 @@
           <t>OSINT; Dark web; Illicit markets; Intelligence Services; Law Enforcement; Online dataset; Online Forums; Investigation workflow; Dark Web Underground Sources; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
+      <c r="U134" t="n">
+        <v/>
+      </c>
+      <c r="V134" t="n">
+        <v/>
+      </c>
+      <c r="W134" t="n">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15562,9 +16508,15 @@
           <t>Social media; General; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
+      <c r="U135" t="n">
+        <v/>
+      </c>
+      <c r="V135" t="n">
+        <v/>
+      </c>
+      <c r="W135" t="n">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15653,9 +16605,15 @@
           <t>Cyber threat intelligence; Geolocation; Image; Law Enforcement; Intelligence Services; Online dataset; CTI; AI</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
+      <c r="U136" t="n">
+        <v/>
+      </c>
+      <c r="V136" t="n">
+        <v/>
+      </c>
+      <c r="W136" t="n">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15744,9 +16702,15 @@
           <t>Social media; Public Health; Law Enforcement; AI; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
+      <c r="U137" t="n">
+        <v/>
+      </c>
+      <c r="V137" t="n">
+        <v/>
+      </c>
+      <c r="W137" t="n">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15835,9 +16799,15 @@
           <t>Cyber threat intelligence; Social media; Hate speech; Law enforcement; Intelligence Services; Goverment Departments; Non-Goverment Organisations; CTI</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
+      <c r="U138" t="n">
+        <v/>
+      </c>
+      <c r="V138" t="n">
+        <v/>
+      </c>
+      <c r="W138" t="n">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15930,9 +16900,15 @@
           <t>Cyber threat intelligence; Social media; Misinformation; Law enforcement; Intelligence Services; Goverment Departments; Non-Goverment Organisations; CTI</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr"/>
-      <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
+      <c r="U139" t="n">
+        <v/>
+      </c>
+      <c r="V139" t="n">
+        <v/>
+      </c>
+      <c r="W139" t="n">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16023,9 +16999,15 @@
           <t>Social media; Law Enforcement; Emergency Services; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
+      <c r="U140" t="n">
+        <v/>
+      </c>
+      <c r="V140" t="n">
+        <v/>
+      </c>
+      <c r="W140" t="n">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16114,9 +17096,15 @@
           <t>Social media; General; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
+      <c r="U141" t="n">
+        <v/>
+      </c>
+      <c r="V141" t="n">
+        <v/>
+      </c>
+      <c r="W141" t="n">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16209,9 +17197,15 @@
           <t>Social media; General; Threat Detection Prediction; SOCMINT</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
+      <c r="U142" t="n">
+        <v/>
+      </c>
+      <c r="V142" t="n">
+        <v/>
+      </c>
+      <c r="W142" t="n">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16300,9 +17294,15 @@
           <t>Social media; General; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
+      <c r="U143" t="n">
+        <v/>
+      </c>
+      <c r="V143" t="n">
+        <v/>
+      </c>
+      <c r="W143" t="n">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16391,9 +17391,15 @@
           <t>Social media; General; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr"/>
+      <c r="U144" t="n">
+        <v/>
+      </c>
+      <c r="V144" t="n">
+        <v/>
+      </c>
+      <c r="W144" t="n">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16486,9 +17492,15 @@
           <t>Social media; General; Threat Detection Prediction; SOCMINT</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
+      <c r="U145" t="n">
+        <v/>
+      </c>
+      <c r="V145" t="n">
+        <v/>
+      </c>
+      <c r="W145" t="n">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16579,9 +17591,15 @@
           <t>OSINT; Social media; General; Web Pages; Oline Forums; Blogs; Online dataset; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr"/>
-      <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
+      <c r="U146" t="n">
+        <v/>
+      </c>
+      <c r="V146" t="n">
+        <v/>
+      </c>
+      <c r="W146" t="n">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16670,9 +17688,15 @@
           <t>Social media; Emergency Services; Law Enforcement; Goverment Departments; Network analysis; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr"/>
-      <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
+      <c r="U147" t="n">
+        <v/>
+      </c>
+      <c r="V147" t="n">
+        <v/>
+      </c>
+      <c r="W147" t="n">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16761,9 +17785,15 @@
           <t>Social media; Goverment Departments; Non Goverment Organisations; Intelligence Services; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
+      <c r="U148" t="n">
+        <v/>
+      </c>
+      <c r="V148" t="n">
+        <v/>
+      </c>
+      <c r="W148" t="n">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16858,9 +17888,15 @@
           <t>Other; Law Enforcement; Websites; Evidence; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
+      <c r="U149" t="n">
+        <v/>
+      </c>
+      <c r="V149" t="n">
+        <v/>
+      </c>
+      <c r="W149" t="n">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16951,9 +17987,15 @@
           <t>Social media; Dark web; Illicit markets; General; Online Marketplaces; Online Forums; Blogs; Dark Web Underground Sources; SOCMINT</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
+      <c r="U150" t="n">
+        <v/>
+      </c>
+      <c r="V150" t="n">
+        <v/>
+      </c>
+      <c r="W150" t="n">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17048,9 +18090,15 @@
           <t>Social media; General; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr"/>
-      <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
+      <c r="U151" t="n">
+        <v/>
+      </c>
+      <c r="V151" t="n">
+        <v/>
+      </c>
+      <c r="W151" t="n">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17143,9 +18191,15 @@
           <t>Cyber threat intelligence; Social media; Misinformation; Intelligence Services; Law Enforcement; Non-Goverment Organisations; Goverment Departments; Online Dataset; CTI</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
+      <c r="U152" t="n">
+        <v/>
+      </c>
+      <c r="V152" t="n">
+        <v/>
+      </c>
+      <c r="W152" t="n">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17238,9 +18292,15 @@
           <t>Cyber threat intelligence; Social media; General; Twitter; CTI; AI</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr"/>
-      <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
+      <c r="U153" t="n">
+        <v/>
+      </c>
+      <c r="V153" t="n">
+        <v/>
+      </c>
+      <c r="W153" t="n">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17329,9 +18389,15 @@
           <t>Social media; General; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
+      <c r="U154" t="n">
+        <v/>
+      </c>
+      <c r="V154" t="n">
+        <v/>
+      </c>
+      <c r="W154" t="n">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17424,9 +18490,15 @@
           <t>Social media; Healthcare; Goverment Departments; AI; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr"/>
-      <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr"/>
+      <c r="U155" t="n">
+        <v/>
+      </c>
+      <c r="V155" t="n">
+        <v/>
+      </c>
+      <c r="W155" t="n">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17519,9 +18591,15 @@
           <t>OSINT; Social media; Network analysis; Law Enforcement; Government Departments; Intelligence Services; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr"/>
+      <c r="U156" t="n">
+        <v/>
+      </c>
+      <c r="V156" t="n">
+        <v/>
+      </c>
+      <c r="W156" t="n">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17610,9 +18688,15 @@
           <t>Cyber threat intelligence; Social media; Healthcare; Goverment Departments; CTI</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr"/>
-      <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
+      <c r="U157" t="n">
+        <v/>
+      </c>
+      <c r="V157" t="n">
+        <v/>
+      </c>
+      <c r="W157" t="n">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17707,9 +18791,15 @@
           <t>Social media; Network analysis; Law Enforcement; Intelligence Services; Investigative Workflows Collaboration; Other</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr"/>
+      <c r="U158" t="n">
+        <v/>
+      </c>
+      <c r="V158" t="n">
+        <v/>
+      </c>
+      <c r="W158" t="n">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17804,9 +18894,15 @@
           <t>Social media; General; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr"/>
+      <c r="U159" t="n">
+        <v/>
+      </c>
+      <c r="V159" t="n">
+        <v/>
+      </c>
+      <c r="W159" t="n">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17897,9 +18993,15 @@
           <t>Social media; General; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
+      <c r="U160" t="n">
+        <v/>
+      </c>
+      <c r="V160" t="n">
+        <v/>
+      </c>
+      <c r="W160" t="n">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17994,9 +19096,15 @@
           <t>Cyber threat intelligence; Cyber Risk Management; Security Operations; Intelligence Services; Government Services; Online dataset; CTI</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
-      <c r="W161" t="inlineStr"/>
+      <c r="U161" t="n">
+        <v/>
+      </c>
+      <c r="V161" t="n">
+        <v/>
+      </c>
+      <c r="W161" t="n">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18091,9 +19199,15 @@
           <t>Cyber threat intelligence; Social media; Cyber harassment; Law Enforcement; Non Goverment Organisations; CTI</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
-      <c r="W162" t="inlineStr"/>
+      <c r="U162" t="n">
+        <v/>
+      </c>
+      <c r="V162" t="n">
+        <v/>
+      </c>
+      <c r="W162" t="n">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18186,9 +19300,15 @@
           <t>Cyber threat intelligence; Social media; Hate speech; Law Enforcement; Inteligence Services; Government Departments; Non-Goverment Organisations; CTI</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
-      <c r="W163" t="inlineStr"/>
+      <c r="U163" t="n">
+        <v/>
+      </c>
+      <c r="V163" t="n">
+        <v/>
+      </c>
+      <c r="W163" t="n">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18283,9 +19403,15 @@
           <t>Cyber threat intelligence; Social media; Misinformation; Intelligence Services; Law Enforcement; Non-Goverment Organisations; Goverment Departments; Online News; CTI; Network analysis</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
-      <c r="W164" t="inlineStr"/>
+      <c r="U164" t="n">
+        <v/>
+      </c>
+      <c r="V164" t="n">
+        <v/>
+      </c>
+      <c r="W164" t="n">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18374,9 +19500,15 @@
           <t>Social media; General; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr"/>
-      <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
+      <c r="U165" t="n">
+        <v/>
+      </c>
+      <c r="V165" t="n">
+        <v/>
+      </c>
+      <c r="W165" t="n">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18469,9 +19601,15 @@
           <t>Cyber threat intelligence; Social media; Intelligence Services; Law Enforcement; CTI; AI</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr"/>
-      <c r="W166" t="inlineStr"/>
+      <c r="U166" t="n">
+        <v/>
+      </c>
+      <c r="V166" t="n">
+        <v/>
+      </c>
+      <c r="W166" t="n">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18564,9 +19702,15 @@
           <t>Social media; General; Foundations Reviews; Other</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr"/>
-      <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr"/>
+      <c r="U167" t="n">
+        <v/>
+      </c>
+      <c r="V167" t="n">
+        <v/>
+      </c>
+      <c r="W167" t="n">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18659,9 +19803,15 @@
           <t>Cyber threat intelligence; Social media; General; CTI</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
+      <c r="U168" t="n">
+        <v/>
+      </c>
+      <c r="V168" t="n">
+        <v/>
+      </c>
+      <c r="W168" t="n">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18756,9 +19906,15 @@
           <t>Social media; General; Online Dataset; Network analysis; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
-      <c r="W169" t="inlineStr"/>
+      <c r="U169" t="n">
+        <v/>
+      </c>
+      <c r="V169" t="n">
+        <v/>
+      </c>
+      <c r="W169" t="n">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18849,9 +20005,15 @@
           <t>Social media; General; Online Dataset; AI; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
-      <c r="W170" t="inlineStr"/>
+      <c r="U170" t="n">
+        <v/>
+      </c>
+      <c r="V170" t="n">
+        <v/>
+      </c>
+      <c r="W170" t="n">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18944,9 +20106,15 @@
           <t>Social media; General; Online Dataset; Social Media OSINT Collection; Other</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
+      <c r="U171" t="n">
+        <v/>
+      </c>
+      <c r="V171" t="n">
+        <v/>
+      </c>
+      <c r="W171" t="n">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19035,9 +20203,15 @@
           <t>Malicious infrastructure; General; Online Dataset; Malicious Infrastructure Exploit Discovery; Infrastructure Indicator Analysis</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
+      <c r="U172" t="n">
+        <v/>
+      </c>
+      <c r="V172" t="n">
+        <v/>
+      </c>
+      <c r="W172" t="n">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19126,9 +20300,15 @@
           <t>OSINT; AI OSINT ethics; Foundations; Foundations Reviews; Other</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr"/>
-      <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
+      <c r="U173" t="n">
+        <v/>
+      </c>
+      <c r="V173" t="n">
+        <v/>
+      </c>
+      <c r="W173" t="n">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19219,9 +20399,15 @@
           <t>OSINT; AI OSINT; Foundations; AI; Foundations Reviews; Other</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr"/>
+      <c r="U174" t="n">
+        <v/>
+      </c>
+      <c r="V174" t="n">
+        <v/>
+      </c>
+      <c r="W174" t="n">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19310,9 +20496,15 @@
           <t>Cyber threat intelligence; Social media; SOCMINT; SOCMINT analytics; Foundations; CTI; Foundations Reviews</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr"/>
-      <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
+      <c r="U175" t="n">
+        <v/>
+      </c>
+      <c r="V175" t="n">
+        <v/>
+      </c>
+      <c r="W175" t="n">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19401,9 +20593,15 @@
           <t>Risk assessment; Foundations; Foundations Reviews; Other</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr"/>
-      <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr"/>
+      <c r="U176" t="n">
+        <v/>
+      </c>
+      <c r="V176" t="n">
+        <v/>
+      </c>
+      <c r="W176" t="n">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19492,9 +20690,15 @@
           <t>Geolocation; Image; Geolocation crowdsourcing; Collaborative OSINT; Investigation workflow; Investigative Workflows Collaboration; Image Geolocation</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr"/>
-      <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr"/>
+      <c r="U177" t="n">
+        <v/>
+      </c>
+      <c r="V177" t="n">
+        <v/>
+      </c>
+      <c r="W177" t="n">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19583,9 +20787,15 @@
           <t>Collaboration; Collaborative OSINT; Investigation workflow; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr"/>
+      <c r="U178" t="n">
+        <v/>
+      </c>
+      <c r="V178" t="n">
+        <v/>
+      </c>
+      <c r="W178" t="n">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19674,9 +20884,15 @@
           <t>Social dynamics; Collaborative OSINT; OSINT; Investigation workflow; Other; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
-      <c r="W179" t="inlineStr"/>
+      <c r="U179" t="n">
+        <v/>
+      </c>
+      <c r="V179" t="n">
+        <v/>
+      </c>
+      <c r="W179" t="n">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19765,9 +20981,15 @@
           <t>Crowdsourcing; Collaborative OSINT; Investigation workflow; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr"/>
-      <c r="V180" t="inlineStr"/>
-      <c r="W180" t="inlineStr"/>
+      <c r="U180" t="n">
+        <v/>
+      </c>
+      <c r="V180" t="n">
+        <v/>
+      </c>
+      <c r="W180" t="n">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19856,9 +21078,15 @@
           <t>OSINT; Social media; Misinformation; Training; Collaborative OSINT; Investigation workflow; Social Media OSINT Collection; SOCMINT</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr"/>
-      <c r="V181" t="inlineStr"/>
-      <c r="W181" t="inlineStr"/>
+      <c r="U181" t="n">
+        <v/>
+      </c>
+      <c r="V181" t="n">
+        <v/>
+      </c>
+      <c r="W181" t="n">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19947,9 +21175,15 @@
           <t>Case study; Collaborative OSINT; Investigation workflow; Investigative Workflows Collaboration; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
-      <c r="W182" t="inlineStr"/>
+      <c r="U182" t="n">
+        <v/>
+      </c>
+      <c r="V182" t="n">
+        <v/>
+      </c>
+      <c r="W182" t="n">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20038,9 +21272,15 @@
           <t>Cyber threat intelligence; Social media; Bellingcat; Investigative Journalism; CTI</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
-      <c r="W183" t="inlineStr"/>
+      <c r="U183" t="n">
+        <v/>
+      </c>
+      <c r="V183" t="n">
+        <v/>
+      </c>
+      <c r="W183" t="n">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20129,9 +21369,15 @@
           <t>Evidence; Investigative Journalism; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
-      <c r="W184" t="inlineStr"/>
+      <c r="U184" t="n">
+        <v/>
+      </c>
+      <c r="V184" t="n">
+        <v/>
+      </c>
+      <c r="W184" t="n">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20220,9 +21466,15 @@
           <t>Human rights; Investigative Journalism; Investigation workflow; Other; Investigative Workflow</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr"/>
-      <c r="V185" t="inlineStr"/>
-      <c r="W185" t="inlineStr"/>
+      <c r="U185" t="n">
+        <v/>
+      </c>
+      <c r="V185" t="n">
+        <v/>
+      </c>
+      <c r="W185" t="n">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20311,9 +21563,15 @@
           <t>Geolocation; Image; Visual evidence; Investigative Journalism; Evidence; Investigation workflow; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr"/>
-      <c r="W186" t="inlineStr"/>
+      <c r="U186" t="n">
+        <v/>
+      </c>
+      <c r="V186" t="n">
+        <v/>
+      </c>
+      <c r="W186" t="n">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20402,9 +21660,15 @@
           <t>Legal evidence; Investigative Journalism; Evidence; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr"/>
-      <c r="W187" t="inlineStr"/>
+      <c r="U187" t="n">
+        <v/>
+      </c>
+      <c r="V187" t="n">
+        <v/>
+      </c>
+      <c r="W187" t="n">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20493,9 +21757,15 @@
           <t>Policy; Investigative Journalism; Other</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr"/>
-      <c r="W188" t="inlineStr"/>
+      <c r="U188" t="n">
+        <v/>
+      </c>
+      <c r="V188" t="n">
+        <v/>
+      </c>
+      <c r="W188" t="n">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20586,9 +21856,15 @@
           <t>Digital forensics; Forensics; OSINT; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr"/>
-      <c r="V189" t="inlineStr"/>
-      <c r="W189" t="inlineStr"/>
+      <c r="U189" t="n">
+        <v/>
+      </c>
+      <c r="V189" t="n">
+        <v/>
+      </c>
+      <c r="W189" t="n">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20677,9 +21953,15 @@
           <t>Social media; Digital forensics; Chain of custody; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr"/>
-      <c r="V190" t="inlineStr"/>
-      <c r="W190" t="inlineStr"/>
+      <c r="U190" t="n">
+        <v/>
+      </c>
+      <c r="V190" t="n">
+        <v/>
+      </c>
+      <c r="W190" t="n">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20768,9 +22050,15 @@
           <t>Digital forensics; Multimedia forensics; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr"/>
-      <c r="W191" t="inlineStr"/>
+      <c r="U191" t="n">
+        <v/>
+      </c>
+      <c r="V191" t="n">
+        <v/>
+      </c>
+      <c r="W191" t="n">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20859,9 +22147,15 @@
           <t>Digital forensics; Evidence usage; Evidence; Foundations Reviews; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr"/>
-      <c r="W192" t="inlineStr"/>
+      <c r="U192" t="n">
+        <v/>
+      </c>
+      <c r="V192" t="n">
+        <v/>
+      </c>
+      <c r="W192" t="n">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20950,9 +22244,15 @@
           <t>Social media; Geolocation; Image; Geolocation Network Analysis; Foundations Reviews; SOCMINT</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr"/>
-      <c r="W193" t="inlineStr"/>
+      <c r="U193" t="n">
+        <v/>
+      </c>
+      <c r="V193" t="n">
+        <v/>
+      </c>
+      <c r="W193" t="n">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21041,9 +22341,15 @@
           <t>Network analysis; Geolocation Network Analysis; Investigative Workflows Collaboration; Image Geolocation</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr"/>
-      <c r="W194" t="inlineStr"/>
+      <c r="U194" t="n">
+        <v/>
+      </c>
+      <c r="V194" t="n">
+        <v/>
+      </c>
+      <c r="W194" t="n">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21132,9 +22438,15 @@
           <t>Criminal networks; Geolocation Network Analysis; Network analysis; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr"/>
-      <c r="W195" t="inlineStr"/>
+      <c r="U195" t="n">
+        <v/>
+      </c>
+      <c r="V195" t="n">
+        <v/>
+      </c>
+      <c r="W195" t="n">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21223,9 +22535,15 @@
           <t>Cyber threat intelligence; Geospatial analysis; Geolocation Network Analysis; CTI</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr"/>
-      <c r="W196" t="inlineStr"/>
+      <c r="U196" t="n">
+        <v/>
+      </c>
+      <c r="V196" t="n">
+        <v/>
+      </c>
+      <c r="W196" t="n">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21314,9 +22632,15 @@
           <t>Cyber threat intelligence; Network analysis; Network construction; Geolocation Network Analysis; OSINT; CTI</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr"/>
-      <c r="W197" t="inlineStr"/>
+      <c r="U197" t="n">
+        <v/>
+      </c>
+      <c r="V197" t="n">
+        <v/>
+      </c>
+      <c r="W197" t="n">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21405,9 +22729,15 @@
           <t>Network inference; Other; Network analysis</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr"/>
-      <c r="W198" t="inlineStr"/>
+      <c r="U198" t="n">
+        <v/>
+      </c>
+      <c r="V198" t="n">
+        <v/>
+      </c>
+      <c r="W198" t="n">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21496,9 +22826,15 @@
           <t>Cyber threat intelligence; Network metrics; Other; CTI</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr"/>
-      <c r="W199" t="inlineStr"/>
+      <c r="U199" t="n">
+        <v/>
+      </c>
+      <c r="V199" t="n">
+        <v/>
+      </c>
+      <c r="W199" t="n">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21587,9 +22923,15 @@
           <t>Semantic analysis; Other</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr"/>
-      <c r="W200" t="inlineStr"/>
+      <c r="U200" t="n">
+        <v/>
+      </c>
+      <c r="V200" t="n">
+        <v/>
+      </c>
+      <c r="W200" t="n">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21678,9 +23020,15 @@
           <t>Cyber threat intelligence; Email analysis; Other; CTI</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr"/>
-      <c r="W201" t="inlineStr"/>
+      <c r="U201" t="n">
+        <v/>
+      </c>
+      <c r="V201" t="n">
+        <v/>
+      </c>
+      <c r="W201" t="n">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21699,10 +23047,8 @@
       <c r="D202" t="n">
         <v>2022</v>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="E202" t="n">
+        <v/>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21740,10 +23086,8 @@
           <t>Expanded</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="N202" t="n">
+        <v/>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -21775,12 +23119,14 @@
           <t>Cyber threat intelligence; CTI evaluation; Other; CTI; Threat intelligence</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr"/>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="U202" t="n">
+        <v/>
+      </c>
+      <c r="V202" t="n">
+        <v/>
+      </c>
+      <c r="W202" t="n">
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -21800,10 +23146,8 @@
       <c r="D203" t="n">
         <v>2024</v>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="E203" t="n">
+        <v/>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21841,10 +23185,8 @@
           <t>Expanded</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="N203" t="n">
+        <v/>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -21874,12 +23216,14 @@
           <t>Cyber threat intelligence; CTI NLP; Other; CTI; Threat intelligence</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr"/>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="U203" t="n">
+        <v/>
+      </c>
+      <c r="V203" t="n">
+        <v/>
+      </c>
+      <c r="W203" t="n">
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -22006,10 +23350,8 @@
       <c r="D205" t="n">
         <v>2024</v>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="E205" t="n">
+        <v/>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22047,10 +23389,8 @@
           <t>Expanded</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="N205" t="n">
+        <v/>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -22080,12 +23420,14 @@
           <t>OSINT; Cyber threat intelligence; AI OSINT; Other; CTI; AI</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr"/>
-      <c r="V205" t="inlineStr"/>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="U205" t="n">
+        <v/>
+      </c>
+      <c r="V205" t="n">
+        <v/>
+      </c>
+      <c r="W205" t="n">
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -22105,10 +23447,8 @@
       <c r="D206" t="n">
         <v>2012</v>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="E206" t="n">
+        <v/>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22146,10 +23486,8 @@
           <t>Expanded</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="N206" t="n">
+        <v/>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -22179,12 +23517,14 @@
           <t>Linguistic analysis; Other; Digital Forensics Evidence</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr"/>
-      <c r="V206" t="inlineStr"/>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
+      <c r="U206" t="n">
+        <v/>
+      </c>
+      <c r="V206" t="n">
+        <v/>
+      </c>
+      <c r="W206" t="n">
+        <v/>
       </c>
     </row>
     <row r="207">
